--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,13 +269,13 @@
     <t>ArTransaction433.intcharge</t>
   </si>
   <si>
-    <t>INT.CHARGE (-25)</t>
+    <t>INT.CHARGE (-27)</t>
   </si>
   <si>
     <t>ArTransaction433.admcharge</t>
   </si>
   <si>
-    <t>ADM.CHARGE (-25)</t>
+    <t>ADM.CHARGE (-28)</t>
   </si>
   <si>
     <t>ArTransaction433.dateEntered</t>
@@ -300,18 +300,18 @@
     <t>TRANSACTION NUMBER (-.01)</t>
   </si>
   <si>
+    <t>ArTransaction433.billNumber</t>
+  </si>
+  <si>
+    <t>BILL NUMBER (-.03)</t>
+  </si>
+  <si>
     <t>ArTransaction433.transactionDate</t>
   </si>
   <si>
     <t>TRANSACTION DATE (-11)</t>
   </si>
   <si>
-    <t>ArTransaction433.billNumber</t>
-  </si>
-  <si>
-    <t>BILL NUMBER (-.03)</t>
-  </si>
-  <si>
     <t>ArTransaction433.transAmount</t>
   </si>
   <si>
@@ -324,10 +324,10 @@
     <t>RECEIPT # (-13)</t>
   </si>
   <si>
-    <t>ArTransaction433.prinCollected</t>
-  </si>
-  <si>
-    <t>PRIN. COLLECTED (-31)</t>
+    <t>ArTransaction433.princollected</t>
+  </si>
+  <si>
+    <t>PRIN.COLLECTED (-31)</t>
   </si>
   <si>
     <t>ArTransaction433.interestCollected</t>
@@ -336,10 +336,10 @@
     <t>INTEREST COLLECTED (-32)</t>
   </si>
   <si>
-    <t>ArTransaction433.adminCollected</t>
-  </si>
-  <si>
-    <t>ADMIN. COLLECTED (-33)</t>
+    <t>ArTransaction433.admincollected</t>
+  </si>
+  <si>
+    <t>ADMIN.COLLECTED (-33)</t>
   </si>
   <si>
     <t>ArTransaction433.marshalFeeCollected</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="113">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -301,6 +301,10 @@
   </si>
   <si>
     <t>ArTransaction433.billNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/AccountsReceivable430)
+</t>
   </si>
   <si>
     <t>BILL NUMBER (-.03)</t>
@@ -1631,13 +1635,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1705,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1734,10 +1738,10 @@
         <v>79</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1788,7 +1792,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1805,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1834,10 +1838,10 @@
         <v>79</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1888,7 +1892,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1905,10 +1909,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1934,10 +1938,10 @@
         <v>79</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1988,7 +1992,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -2005,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2034,10 +2038,10 @@
         <v>79</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2088,7 +2092,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
@@ -2105,10 +2109,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2134,10 +2138,10 @@
         <v>79</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2188,7 +2192,7 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>73</v>
@@ -2205,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2234,10 +2238,10 @@
         <v>79</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2288,7 +2292,7 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
@@ -2305,10 +2309,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2334,10 +2338,10 @@
         <v>79</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2388,7 +2392,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2405,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2434,10 +2438,10 @@
         <v>79</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2488,7 +2492,7 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ArTransaction433.xlsx
+++ b/docs/StructureDefinition-ArTransaction433.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
